--- a/etf_holdings/2026-10-11_errors.xlsx
+++ b/etf_holdings/2026-10-11_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,24 +441,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-11 23:00:43</t>
+          <t>2026-10-11 23:04:47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00981A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:05:47</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00991A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:08:30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00993A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/etf_holdings/2026-10-11_errors.xlsx
+++ b/etf_holdings/2026-10-11_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,24 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-11 23:04:47</t>
+          <t>2026-10-11 23:40:12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00981A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00982A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -466,49 +466,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-11 23:05:47</t>
+          <t>2026-10-11 23:41:51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00991A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-10-11 23:08:30</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00993A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
